--- a/JsonConverter/ExcelFiles/Loading.xlsx
+++ b/JsonConverter/ExcelFiles/Loading.xlsx
@@ -19,36 +19,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <x:si>
-    <x:t>인사팀장</x:t>
+    <x:t>로딩 텍스트</x:t>
   </x:si>
   <x:si>
-    <x:t>다음 대사 ID</x:t>
+    <x:t>Loading_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Background</x:t>
+    <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+    <x:t>Loading_05</x:t>
   </x:si>
   <x:si>
-    <x:t>배경</x:t>
+    <x:t>Loading_02</x:t>
   </x:si>
   <x:si>
-    <x:t>BGM</x:t>
+    <x:t>Loading_06</x:t>
   </x:si>
   <x:si>
-    <x:t>SFX</x:t>
+    <x:t>Loading_03</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터</x:t>
+    <x:t>Loading_08</x:t>
   </x:si>
   <x:si>
-    <x:t>대사</x:t>
+    <x:t>Loading_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
@@ -57,142 +69,22 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
     <x:t>Content</x:t>
   </x:si>
   <x:si>
-    <x:t>대사 ID</x:t>
+    <x:t>어쩌구 저쩌구 일해라 절해라 이래라 저래라 전투 관련 어쩔저쩔</x:t>
   </x:si>
   <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
+    <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
+    <x:t>타이쿤을 설치하는 데에는 무려 엄청나게 많은 돈이 들어갑니다. 어절씨구</x:t>
   </x:si>
   <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
+    <x:t>0000은 전성기에 굉장히 잘 나갔습니다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -996,96 +888,58 @@
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
-    <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
+    <x:col min="2" max="2" width="168.71484375" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="13.85546875" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="120" style="3" customWidth="1"/>
+    <x:col min="4" max="4" width="11.85546875" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
     <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
     <x:col min="7" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="10"/>
+      <x:c r="D3" s="12"/>
+      <x:c r="E3" s="12"/>
+      <x:c r="F3" s="13"/>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="4" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D3" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
+      <x:c r="B4" s="4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
+      <x:c r="C4" s="4"/>
+      <x:c r="D4" s="5"/>
       <x:c r="E4" s="5"/>
       <x:c r="F4" s="14"/>
       <x:c r="G4" s="5"/>
@@ -1100,17 +954,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>18</x:v>
       </x:c>
-      <x:c r="C5" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C5" s="4"/>
+      <x:c r="D5" s="5"/>
       <x:c r="E5" s="5"/>
       <x:c r="F5" s="14"/>
       <x:c r="G5" s="5"/>
@@ -1124,18 +974,14 @@
       <x:c r="O5" s="5"/>
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="6" t="s">
-        <x:v>47</x:v>
+      <x:c r="A6" s="4" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>55</x:v>
-      </x:c>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="5"/>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>
@@ -1149,18 +995,14 @@
       <x:c r="O6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="6" t="s">
-        <x:v>42</x:v>
+      <x:c r="A7" s="4" t="s">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="5"/>
       <x:c r="E7" s="5"/>
       <x:c r="F7" s="5"/>
       <x:c r="G7" s="5"/>
@@ -1174,18 +1016,14 @@
       <x:c r="O7" s="5"/>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="6" t="s">
-        <x:v>49</x:v>
+      <x:c r="A8" s="4" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
-      <x:c r="C8" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
+      <x:c r="C8" s="4"/>
+      <x:c r="D8" s="15"/>
       <x:c r="E8" s="5"/>
       <x:c r="F8" s="5"/>
       <x:c r="G8" s="5"/>
@@ -1199,18 +1037,14 @@
       <x:c r="O8" s="5"/>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6" t="s">
-        <x:v>38</x:v>
+      <x:c r="A9" s="4" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>12</x:v>
       </x:c>
-      <x:c r="C9" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
+      <x:c r="C9" s="4"/>
+      <x:c r="D9" s="5"/>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
       <x:c r="G9" s="5"/>
@@ -1224,18 +1058,14 @@
       <x:c r="O9" s="5"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="6" t="s">
-        <x:v>39</x:v>
+      <x:c r="A10" s="4" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>3</x:v>
       </x:c>
-      <x:c r="C10" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
+      <x:c r="C10" s="4"/>
+      <x:c r="D10" s="5"/>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5"/>
       <x:c r="G10" s="5"/>
@@ -1249,18 +1079,14 @@
       <x:c r="O10" s="5"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="6" t="s">
-        <x:v>40</x:v>
+      <x:c r="A11" s="4" t="s">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
+      <x:c r="C11" s="6"/>
+      <x:c r="D11" s="15"/>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
       <x:c r="G11" s="5"/>
@@ -1274,18 +1100,10 @@
       <x:c r="O11" s="5"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B12" s="4" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C12" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="15"/>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
       <x:c r="G12" s="5"/>
@@ -1299,18 +1117,10 @@
       <x:c r="O12" s="5"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B13" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C13" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="5"/>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
       <x:c r="G13" s="5"/>
@@ -1324,18 +1134,10 @@
       <x:c r="O13" s="5"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="6" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="5"/>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5"/>
       <x:c r="G14" s="5"/>
@@ -1349,18 +1151,10 @@
       <x:c r="O14" s="5"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="6" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B15" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="4"/>
+      <x:c r="C15" s="6"/>
+      <x:c r="D15" s="15"/>
       <x:c r="E15" s="5"/>
       <x:c r="F15" s="5"/>
       <x:c r="G15" s="5"/>
@@ -1374,131 +1168,59 @@
       <x:c r="O15" s="5"/>
     </x:row>
     <x:row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A16" s="6" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B16" s="4" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D16" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="6"/>
+      <x:c r="D16" s="5"/>
     </x:row>
     <x:row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A17" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B17" s="4" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C17" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="15"/>
     </x:row>
     <x:row r="18" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A18" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B18" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="5"/>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="6" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C19" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="6"/>
+      <x:c r="D19" s="15"/>
       <x:c r="E19" s="5"/>
     </x:row>
     <x:row r="20" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A20" s="6" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B20" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C20" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="15"/>
     </x:row>
     <x:row r="21" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A21" s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C21" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
+      <x:c r="A21" s="4"/>
+      <x:c r="B21" s="4"/>
+      <x:c r="C21" s="4"/>
+      <x:c r="D21" s="5"/>
     </x:row>
     <x:row r="22" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A22" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B22" s="4" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C22" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="5" t="s">
-        <x:v>56</x:v>
-      </x:c>
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="5"/>
     </x:row>
     <x:row r="23" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A23" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B23" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C23" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="A23" s="6"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="6"/>
+      <x:c r="D23" s="15"/>
     </x:row>
     <x:row r="24" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A24" s="6" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B24" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
+      <x:c r="A24" s="6"/>
+      <x:c r="B24" s="7"/>
+      <x:c r="C24" s="6"/>
+      <x:c r="D24" s="5"/>
     </x:row>
     <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A25" s="7"/>

--- a/JsonConverter/ExcelFiles/Loading.xlsx
+++ b/JsonConverter/ExcelFiles/Loading.xlsx
@@ -21,46 +21,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <x:si>
-    <x:t>로딩 텍스트</x:t>
+    <x:t>어쩌구 저쩌구 일해라 절해라 이래라 저래라 전투 관련 어쩔저쩔</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_01</x:t>
+    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이쿤을 설치하는 데에는 무려 엄청나게 많은 돈이 들어갑니다. 어절씨구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
   </x:si>
   <x:si>
     <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
+    <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_05</x:t>
+    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
+    <x:t>Content</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
@@ -69,19 +72,16 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Content</x:t>
+    <x:t>로딩 텍스트</x:t>
   </x:si>
   <x:si>
-    <x:t>어쩌구 저쩌구 일해라 절해라 이래라 저래라 전투 관련 어쩔저쩔</x:t>
+    <x:t>로딩 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
+    <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이쿤을 설치하는 데에는 무려 엄청나게 많은 돈이 들어갑니다. 어절씨구</x:t>
+    <x:t>Loading_1</x:t>
   </x:si>
   <x:si>
     <x:t>0000은 전성기에 굉장히 잘 나갔습니다.</x:t>
@@ -898,10 +898,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="2"/>
@@ -909,10 +909,10 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1"/>
       <x:c r="D2" s="1"/>
@@ -921,10 +921,10 @@
     </x:row>
     <x:row r="3" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="10"/>
       <x:c r="D3" s="12"/>
@@ -933,10 +933,10 @@
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="5"/>
@@ -954,10 +954,10 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="5"/>
@@ -975,7 +975,7 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
         <x:v>21</x:v>
@@ -996,10 +996,10 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
       <x:c r="D7" s="5"/>
@@ -1017,10 +1017,10 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="15"/>
@@ -1038,10 +1038,10 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="4"/>
       <x:c r="D9" s="5"/>
@@ -1059,10 +1059,10 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="4"/>
       <x:c r="D10" s="5"/>
@@ -1080,10 +1080,10 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="6"/>
       <x:c r="D11" s="15"/>

--- a/JsonConverter/ExcelFiles/Loading.xlsx
+++ b/JsonConverter/ExcelFiles/Loading.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <x:si>
-    <x:t>어쩌구 저쩌구 일해라 절해라 이래라 저래라 전투 관련 어쩔저쩔</x:t>
+    <x:t>아무튼 탈인간 실버타운의 모든 영웅들은 전성기에 굉장히 잘 나갔습니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
+    <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>타이쿤을 설치하는 데에는 무려 엄청나게 많은 돈이 들어갑니다. 어절씨구</x:t>
+    <x:t>Loading_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_2</x:t>
   </x:si>
   <x:si>
     <x:t>Loading_8</x:t>
@@ -36,31 +39,22 @@
     <x:t>Loading_6</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_7</x:t>
-  </x:si>
-  <x:si>
     <x:t>Loading_4</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_2</x:t>
+    <x:t>Loading_7</x:t>
   </x:si>
   <x:si>
     <x:t>Loading_5</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_3</x:t>
+    <x:t>Loading_1</x:t>
   </x:si>
   <x:si>
-    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
+    <x:t>로딩 텍스트</x:t>
   </x:si>
   <x:si>
-    <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
+    <x:t>로딩 ID</x:t>
   </x:si>
   <x:si>
     <x:t>Content</x:t>
@@ -72,19 +66,25 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>로딩 텍스트</x:t>
+    <x:t>전투에 승리하기 위해서는 에너지를 효율적으로 사용해야합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>로딩 ID</x:t>
+    <x:t>회복 아이템과 서포트 아이템을 적절하게 사용하면 전투에서 승리할 수 있습니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
+    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_1</x:t>
+    <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>0000은 전성기에 굉장히 잘 나갔습니다.</x:t>
+    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -898,10 +898,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="2"/>
@@ -909,10 +909,10 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1"/>
       <x:c r="D2" s="1"/>
@@ -921,10 +921,10 @@
     </x:row>
     <x:row r="3" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C3" s="10"/>
       <x:c r="D3" s="12"/>
@@ -933,10 +933,10 @@
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="5"/>
@@ -954,10 +954,10 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="5"/>
@@ -975,10 +975,10 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="5"/>
@@ -999,7 +999,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
       <x:c r="D7" s="5"/>
@@ -1020,7 +1020,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="15"/>
@@ -1038,10 +1038,10 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="4"/>
       <x:c r="D9" s="5"/>
@@ -1059,10 +1059,10 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="4"/>
       <x:c r="D10" s="5"/>
@@ -1080,10 +1080,10 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C11" s="6"/>
       <x:c r="D11" s="15"/>

--- a/JsonConverter/ExcelFiles/Loading.xlsx
+++ b/JsonConverter/ExcelFiles/Loading.xlsx
@@ -19,72 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <x:si>
+    <x:t>Loading_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왕년엔 한손에 들던 묠니르도 이젠 두손도 버겁네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이젠 돈을 벌기보단 자아실현 단계에서의 자경활동이죠. 은퇴한지 40년은 됐거든요.</x:t>
+  </x:si>
   <x:si>
     <x:t>아무튼 탈인간 실버타운의 모든 영웅들은 전성기에 굉장히 잘 나갔습니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무라서 좋은 점은 늙어도 재생될 나뭇가지가 있다는 것입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회복 아이템과 서포트 아이템을 적절하게 사용하면 전투에서 승리할 수 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투에 승리하기 위해서는 에너지를 효율적으로 사용해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩 텍스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_10</x:t>
+  </x:si>
+  <x:si>
     <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩 텍스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투에 승리하기 위해서는 에너지를 효율적으로 사용해야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회복 아이템과 서포트 아이템을 적절하게 사용하면 전투에서 승리할 수 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
+    <x:t>할매프로스트는 과거에 굉장히 인기가 많았습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>살을 빼지 않은 대신 느끼함을 얻었습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몇 cc만 더 맞으면 되는 줄 알았는데 반영구가 80ᄁᆞ지 갈줄은 몰랐어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이를 짚고 힘들게 다니는 것 같지만 사실 마법을 집중해서 쓰기 위한 도구일 뿐입니다. 날라다니거든요.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -898,10 +940,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="2"/>
@@ -909,10 +951,10 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C2" s="1"/>
       <x:c r="D2" s="1"/>
@@ -921,10 +963,10 @@
     </x:row>
     <x:row r="3" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="10"/>
       <x:c r="D3" s="12"/>
@@ -933,10 +975,10 @@
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="5"/>
@@ -954,10 +996,10 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="5"/>
@@ -975,10 +1017,10 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="5"/>
@@ -996,10 +1038,10 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
       <x:c r="D7" s="5"/>
@@ -1017,10 +1059,10 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="15"/>
@@ -1038,10 +1080,10 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="4"/>
       <x:c r="D9" s="5"/>
@@ -1059,10 +1101,10 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="4"/>
       <x:c r="D10" s="5"/>
@@ -1080,10 +1122,10 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="6"/>
       <x:c r="D11" s="15"/>
@@ -1100,8 +1142,12 @@
       <x:c r="O11" s="5"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
+      <x:c r="A12" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="15"/>
       <x:c r="E12" s="5"/>
@@ -1117,8 +1163,12 @@
       <x:c r="O12" s="5"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
+      <x:c r="A13" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="5"/>
       <x:c r="E13" s="5"/>
@@ -1134,8 +1184,12 @@
       <x:c r="O13" s="5"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
+      <x:c r="A14" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="5"/>
       <x:c r="E14" s="5"/>
@@ -1151,8 +1205,12 @@
       <x:c r="O14" s="5"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="4"/>
-      <x:c r="B15" s="4"/>
+      <x:c r="A15" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C15" s="6"/>
       <x:c r="D15" s="15"/>
       <x:c r="E15" s="5"/>
@@ -1168,20 +1226,32 @@
       <x:c r="O15" s="5"/>
     </x:row>
     <x:row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
+      <x:c r="A16" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C16" s="6"/>
       <x:c r="D16" s="5"/>
     </x:row>
     <x:row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
+      <x:c r="A17" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="15"/>
     </x:row>
     <x:row r="18" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
+      <x:c r="A18" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="C18" s="4"/>
       <x:c r="D18" s="5"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/Loading.xlsx
+++ b/JsonConverter/ExcelFiles/Loading.xlsx
@@ -21,112 +21,112 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <x:si>
+    <x:t>회복 아이템과 서포트 아이템을 적절하게 사용하면 전투에서 승리할 수 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩 텍스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이를 짚고 힘들게 다니는 것 같지만 사실 마법을 집중해서 쓰기 위한 도구일 뿐입니다. 날라다니거든요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무튼 탈인간 실버타운의 모든 영웅들은 전성기에 굉장히 잘 나갔습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이젠 돈을 벌기보단 자아실현 단계에서의 자경활동이죠. 은퇴한지 40년은 됐거든요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몇 cc만 더 맞으면 되는 줄 알았는데 반영구가 80까지 갈줄은 몰랐어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왕년엔 한손에 들던 묠니르도 이젠 두손도 버겁네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무라서 좋은 점은 늙어도 재생될 나뭇가지가 있다는 것입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투에 승리하기 위해서는 에너지를 효율적으로 사용해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_15</x:t>
+  </x:si>
+  <x:si>
     <x:t>Loading_13</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왕년엔 한손에 들던 묠니르도 이젠 두손도 버겁네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이젠 돈을 벌기보단 자아실현 단계에서의 자경활동이죠. 은퇴한지 40년은 됐거든요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무튼 탈인간 실버타운의 모든 영웅들은 전성기에 굉장히 잘 나갔습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돋보기는 녹내장 질환을 잠깐이나마 없애주어 선호도가 아주 높습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무라서 좋은 점은 늙어도 재생될 나뭇가지가 있다는 것입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회복 아이템과 서포트 아이템을 적절하게 사용하면 전투에서 승리할 수 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_15</x:t>
+    <x:t>Loading_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading_14</x:t>
   </x:si>
   <x:si>
     <x:t>H.B Project는 Heroes Best Project의 약자입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>H.A.V.E.N은 Heroes Ability Valuation &amp; Extraction Network의 약자입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.A.V.E.N은 Heroes Aftercare &amp; Vitality Extension Network의 약자입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투에 승리하기 위해서는 에너지를 효율적으로 사용해야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요양원의 지하 4층에 무엇이 있는지 아무도 모릅니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩 텍스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>할매프로스트는 과거에 굉장히 인기가 많았습니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Loading_9</x:t>
-  </x:si>
-  <x:si>
     <x:t>살을 빼지 않은 대신 느끼함을 얻었습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몇 cc만 더 맞으면 되는 줄 알았는데 반영구가 80ᄁᆞ지 갈줄은 몰랐어요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지팡이를 짚고 힘들게 다니는 것 같지만 사실 마법을 집중해서 쓰기 위한 도구일 뿐입니다. 날라다니거든요.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -940,10 +940,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="2"/>
@@ -951,10 +951,10 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="1"/>
       <x:c r="D2" s="1"/>
@@ -963,10 +963,10 @@
     </x:row>
     <x:row r="3" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>27</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="10"/>
       <x:c r="D3" s="12"/>
@@ -975,7 +975,7 @@
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>12</x:v>
@@ -996,10 +996,10 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="5"/>
@@ -1017,10 +1017,10 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="5"/>
@@ -1038,10 +1038,10 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
       <x:c r="D7" s="5"/>
@@ -1059,10 +1059,10 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="15"/>
@@ -1080,10 +1080,10 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="4"/>
       <x:c r="D9" s="5"/>
@@ -1101,7 +1101,7 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
         <x:v>11</x:v>
@@ -1122,10 +1122,10 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="6"/>
       <x:c r="D11" s="15"/>
@@ -1143,10 +1143,10 @@
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="15"/>
@@ -1164,10 +1164,10 @@
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="5"/>
@@ -1185,10 +1185,10 @@
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="5"/>
@@ -1206,10 +1206,10 @@
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="6"/>
       <x:c r="D15" s="15"/>
@@ -1227,30 +1227,30 @@
     </x:row>
     <x:row r="16" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="6"/>
       <x:c r="D16" s="5"/>
     </x:row>
     <x:row r="17" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="15"/>
     </x:row>
     <x:row r="18" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="4"/>
       <x:c r="D18" s="5"/>
